--- a/scripts/DoAn4_Bemori/test/cases/SCR_DatHangNhanh_Bemori.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/SCR_DatHangNhanh_Bemori.xlsx
@@ -459,7 +459,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.netabooks.vn/</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.netabooks.vn/</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.netabooks.vn/</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.netabooks.vn/</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
